--- a/AAII_Financials/Quarterly/KB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>KB</t>
   </si>
@@ -656,275 +656,281 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2971700</v>
+      </c>
+      <c r="E8" s="3">
         <v>2951300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2851100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2838400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2868900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2647300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2113200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3057800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2827700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2956800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1672700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2608300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2768100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2842500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4810500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3922900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3426200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3272800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3055600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2868000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2765800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2682500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2727100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2755700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2773400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2932200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3083100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3120900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3250700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3318300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3075700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2847200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2825100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2683600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2768900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2712100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2608400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2453800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>9019700</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2233400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1045,53 +1051,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2971700</v>
+      </c>
+      <c r="E10" s="3">
         <v>2951300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2851100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2838400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2868900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2647300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2113200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3057800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2827700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2956800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1672700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2608300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2768100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2842500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1167,8 +1176,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1211,8 +1223,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1333,8 +1346,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1455,52 +1471,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>155100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>40800</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>4800</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1577,130 +1596,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E15" s="3">
         <v>33800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>95000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>45600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>42300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>38400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>113100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>43300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>36600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>28600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>133200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>25800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>26000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>24700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-167200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-151100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-144000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-267900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-172200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-160400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-145400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-157900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-178100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-167800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-157500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-171500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-192200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-165900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-163400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-161400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-108300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-82700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-76600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-72600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-99100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-83600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-77900</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-66900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-259800</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-63200</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1740,252 +1765,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1220100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1159400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1424900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1176300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1292800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1090200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1398300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1256900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1156700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1211500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1483300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1162300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1209400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1201300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3269100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2013800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1607400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1368500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1266500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>876800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>864500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>855500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1032700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1026600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1204100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1226700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1282900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1290600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1319000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1443300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1338900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1142300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1078300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1021000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>923200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>959800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>834800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1019100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3742800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>967500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1751600</v>
+      </c>
+      <c r="E18" s="3">
         <v>1791900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1426200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1662200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1576000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1557100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>714800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1801000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1671100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1745300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>189400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1446000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1558600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1641300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1541400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1909000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1818800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1904300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1789200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1991200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1901300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1827000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1694400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1729100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1569200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1705500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1800200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1830300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1931700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1874900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1736700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1704900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1746800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1662600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1845800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1752400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1773600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1434700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>5276900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1265900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2028,252 +2060,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E20" s="3">
         <v>63300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>390000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>52400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-155300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-9200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>47200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>55900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-48600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>705400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>20500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>32300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>70100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>73800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1521200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-560200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-610400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-445300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1155300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-653600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-651200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-505200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1092400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-519500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-509600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-879800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1163500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-759200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-735900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-813900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1462800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-628600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-652200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-534100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1206300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-696800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-676300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-566000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-2911100</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-580200</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1796300</v>
+      </c>
+      <c r="E21" s="3">
         <v>1762300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1131200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1655400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1773600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1604700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>780700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1788400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1756200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1068500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>302100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1439500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1514500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1592200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>233900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1499900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1352400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1603200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>833800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1526900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1425200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1509800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>811100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1410500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1251100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1033600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>868300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1277300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1402200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1267900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>425500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1202200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1217000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1248000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>789300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1191800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1230000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>935700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2626300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>749100</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2316,8 +2355,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2394,252 +2433,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1764700</v>
+      </c>
+      <c r="E23" s="3">
         <v>1728500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>881200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1609800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1731300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1566300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>626800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1745100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1719700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1039900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>164100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1413700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1488500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1567500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>20200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1348800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1208500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1459000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>633900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1337600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1250000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1321800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>602000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1209600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1059700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>825700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>636700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1071100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1195700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1061000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>274000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1076400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1094600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1128500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>639400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1055600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1097400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>868700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2365800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>685700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>466400</v>
+      </c>
+      <c r="E24" s="3">
         <v>469500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>369400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>431500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>440100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>412500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>180100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>525500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>478100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>254100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>29600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>420400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>346100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>409200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>106200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>356000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>321900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>340600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>194300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>358100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>344600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>370900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>165400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>290000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>295500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>227200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>181900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>271500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>323300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>291200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>112000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>303700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>299300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>315000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>152200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>265900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>213200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>69900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>394600</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>166000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2760,252 +2808,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1298300</v>
+      </c>
+      <c r="E26" s="3">
         <v>1259000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>511800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1178300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1291300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1153800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>446700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1219600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1241600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>785800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>134400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>993300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1142400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1158300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-86000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>992800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>886600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1118400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>439600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>979500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>905500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>950900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>436600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>919500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>764200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>598500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>454800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>799600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>872500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>769800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>161900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>772700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>795300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>813400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>487300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>789700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>884200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>798800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1971200</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>519700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1259300</v>
+      </c>
+      <c r="E27" s="3">
         <v>1213800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>459500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1163900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1244800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1118800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>429500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1195400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1219100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>739600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>131300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>981200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1101600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1125900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>55500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>973300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>862300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1092900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>462800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>958700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>889800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>929700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>429800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>893200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>753500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>588200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>451700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>796500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>872200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>769500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>161600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>772600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>795300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>813300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>487300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>789800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>871300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>783100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1929400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3126,8 +3183,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3248,8 +3308,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3370,8 +3433,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3492,252 +3558,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-63300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-390000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-52400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>155300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>9200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-47200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-55900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>48600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-705400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-20500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-32300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-70100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-73800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1521200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>560200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>610400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>445300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1155300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>653600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>651200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>505200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1092400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>519500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>509600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>879800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1163500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>759200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>735900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>813900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1462800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>628600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>652200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>534100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1206300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>696800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>676300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>566000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>2911100</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>580200</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1286400</v>
+      </c>
+      <c r="E33" s="3">
         <v>1243200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>492800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1200200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1284500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1152500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>463100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1233200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1257200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>775300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>168400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1016900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1138100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1157100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>55500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>973300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>862300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1092900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>462800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>958700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>889800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>929700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>429800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>893200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>753500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>588200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>451700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>796500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>872200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>769500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>161600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>772600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>795300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>813300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>487300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>789800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>871300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>783100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1929400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3858,257 +3933,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1286400</v>
+      </c>
+      <c r="E35" s="3">
         <v>1243200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>492800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1200200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1284500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1152500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>463100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1233200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1257200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>775300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>168400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1016900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1138100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1157100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>55500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>973300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>862300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1092900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>462800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>958700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>889800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>929700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>429800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>893200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>753500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>588200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>451700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>796500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>872200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>769500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>161600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>772600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>795300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>813300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>487300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>789800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>871300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>783100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1929400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4151,8 +4235,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4195,297 +4280,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22925700</v>
+      </c>
+      <c r="E41" s="3">
         <v>17223800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20100000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14867000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22070000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18038100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16658600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16839000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19651800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19867200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19916200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20768400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>20163500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>18482200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24356100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>20072600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>23075600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>22028000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>23257000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>20870900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>18327700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>22310100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>18950500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>19543200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>17332300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>18740400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>17712200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>18703900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>19818700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>17457700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>17030600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>14863300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>16612200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>17677800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>17439700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>20217500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>16866200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>17040600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>16096400</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>15317200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>77536200</v>
+      </c>
+      <c r="E42" s="3">
         <v>74441800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>73473700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>74021300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>71861900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>65673200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>65045200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>64731100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>64014100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>64461600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>66896800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>62179000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>64582700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>62508800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>59654300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>58184900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>54623900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>55547200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>52295400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>49746500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>51118200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>47278100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>49269800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>48058600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>48206500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>50424000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>48228800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>47443300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>45411000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>47146100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>44531600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>43114400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>42447700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>43192000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>31273000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>29706100</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>29751200</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>27604900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>28116300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>15247300</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>985100</v>
+      </c>
+      <c r="E43" s="3">
         <v>929900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9518400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>824400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1008400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>791300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6602500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1147000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>898200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>704000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9111300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>837800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>895400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>590500</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4561,8 +4653,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4605,8 +4700,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4683,53 +4778,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E45" s="3">
         <v>184300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3915800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>179300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>206800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>88300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3246900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>105900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>103100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>88900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3945600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>165800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>173700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>181600</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4805,53 +4903,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>106859700</v>
+      </c>
+      <c r="E46" s="3">
         <v>96319800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>110808200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>92498200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>97581500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>86848000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>94933200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>85091800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>86909300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>87498200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>102877800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>86326300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>89020200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>85160600</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4927,374 +5028,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>89267100</v>
+      </c>
+      <c r="E47" s="3">
         <v>89479900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>95231300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>94805600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>96799600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>89202000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>90221400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>97460900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>93995900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>93506600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>95476000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>88531600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>89316100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>89054000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1021500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>509900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>382100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>361300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>336500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>476900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>344200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>467700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>570900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>687100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>532600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>457600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>508500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>454400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>463700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>461900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>424100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>393600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>301400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>298000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>294900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>294100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>305700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1622300</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1593600</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>2735500</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3279200</v>
+      </c>
+      <c r="E48" s="3">
         <v>3357800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3556400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3656600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3827100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3683600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3648700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4018200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3854000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3951300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3813900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3671900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3763000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3801200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12209700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5614700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5949400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5891700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5816100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5989300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5879400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5870300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11791300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6437600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6047700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6376400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6711100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6422000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6599100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6361400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5369200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4788000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4903500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4215900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4444200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4448300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>4559300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3854900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3944100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>3170000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1030200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1044200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1114900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1269800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1343000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1307400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1331300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1500800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1476700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1459200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1504400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1475400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1485500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1522100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3794200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2413600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2358700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2453900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2449800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2433700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2456800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2448600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4959700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2465600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2351400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2174400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2327100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2255500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2388000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2517400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2314900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2253400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2381100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2427000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2589900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2616500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2666700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>587900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>587100</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>432800</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5415,8 +5528,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5537,130 +5653,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>37201100</v>
+      </c>
+      <c r="E52" s="3">
         <v>34401600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6699800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>30858000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25229200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21130100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6488800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>26314900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22787800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>26229800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7838900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25385600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>24038600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>21394200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>659300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>747300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>439700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>354600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>501200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>274700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>233400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>211100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>231900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>200300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>59000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>28500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>23500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>15300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>17800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>17700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>14000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>17400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>22700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>141100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2013100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1713100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>103700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>167200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5781,130 +5903,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>559785400</v>
+      </c>
+      <c r="E54" s="3">
         <v>545091200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>552762000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>566673700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>576794900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>523082000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>513011000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>567480300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>538630100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>544846000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>551933600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>532206100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>536275500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>530294900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>516498600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>530667600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>507002600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>516808300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>497921900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>487879900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>475310800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>459495000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>451932800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>466239900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>438497000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>441354200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>440757400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>430266000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>438397600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>446536500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>402854200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>386949700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>389203400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>379359000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>384371300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>380871500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>371579500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>342800500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>338106300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>316656300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5947,8 +6075,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5991,175 +6120,179 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>314051700</v>
+      </c>
+      <c r="E57" s="3">
         <v>308166700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>320326000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>319413400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>326653900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>294945700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>294931700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>322472400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>304947700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>311078400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>313483200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>296354600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300727100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>296985500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14972500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>17914700</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>17227200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>20458200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>22099600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>17191800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>14626200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>19356300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>19698800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>19381400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12879900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>18415900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>16302600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>14635000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>12509900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>13188700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>15017400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>13905600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>11945800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>13307600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23259900</v>
+      </c>
+      <c r="E58" s="3">
         <v>22538800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>23691000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20724000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23453900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24977100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>24197000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20600200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21970900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>19796600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>25701400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>25175600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>24508500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>23695300</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6235,175 +6368,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2677200</v>
+      </c>
+      <c r="E59" s="3">
         <v>2791000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3058800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2516600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2300700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2248300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2418600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2822800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2909800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2944200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2659700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2059600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2489800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1594400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4389600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>715600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>680500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>770500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3180300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>413900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>406200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>650500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3232900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3544700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3215600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4064800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3583200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3621400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3606200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4616900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3722600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3421000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3247600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3909800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3276200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3073300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2737000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3537600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>3106500</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>3121300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>339989200</v>
+      </c>
+      <c r="E60" s="3">
         <v>333496800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>351840500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>342654100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>352408500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>322171300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>326297200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>345895400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>329836900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>333831200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>346898600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>323599500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>327736000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>322275200</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6479,252 +6618,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>93344400</v>
+      </c>
+      <c r="E61" s="3">
         <v>90468900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>100346700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>94127400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>94076300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>86283500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>93071600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>93941300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>91130400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>90914600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>98972100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>91450000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>93490800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>95251400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>93366100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>95536600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>90897600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>87545200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>81651600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>79481000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>75547200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>72089200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>70354400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>72102200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>69777900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>67335600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>64473000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>62451800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>63752800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>65135800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>61528300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>57406000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>56894400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>53892200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>54418100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>52829900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>49550000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>44754500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>44530100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>41852900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>84456400</v>
+      </c>
+      <c r="E62" s="3">
         <v>79598400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>56682900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>85007800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>83905900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>72620900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>51534400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>80511700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>72848400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>74498500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>58708800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>71649300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>69598200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>67318700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1945800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>962500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1048200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1534200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1878800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1986500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1736300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1638500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1577900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1663100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1357900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1256500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1325800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1503700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1506600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1461500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1075700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1144700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1055000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1021800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1105100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2956600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2704100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>612500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>663700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>846700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6845,8 +6993,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6967,8 +7118,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7089,130 +7243,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>519296300</v>
+      </c>
+      <c r="E66" s="3">
         <v>504925700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>510622000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>522987000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>531756600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>482248100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>472520100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>521866200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>495217500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>500790900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>506716100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>488488500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>492462800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>487161700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>476850500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>495798400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>472624700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>480891700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>462326400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>452645800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>441691800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>427549100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>420449800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>434507100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>408032200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>410392600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>408003600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>397834400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>405668400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>413942300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>372862900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>358129300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>360150200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>351114600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>354417300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>351197200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>342916800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>314608200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>310208100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>289942200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7255,8 +7415,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7377,8 +7538,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7499,8 +7663,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7621,8 +7788,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7743,130 +7913,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>29787500</v>
+      </c>
+      <c r="E72" s="3">
         <v>30478600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>26555700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>27044500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>27109100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24551600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23562800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26320200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>24542400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>24137300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>24626500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>23758800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>23425800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>22865500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>21691700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>20669500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19841300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>19835900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>19254600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18797500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18056900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>16948300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>16680100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>16901400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>16011300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15855500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>16753100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>16386400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>16138300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15788500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>14517300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13830000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13541100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>12745800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>13238900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>12753300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>11963500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>11341200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>11006300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>10597800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7987,8 +8163,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8109,8 +8288,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8231,130 +8413,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>39319700</v>
+      </c>
+      <c r="E76" s="3">
         <v>38988800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>40905700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>42413400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>43645900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>39543800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>39187000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44120600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41475200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>42513900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>43718700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>42256400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>42268100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>41843100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>39648100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>34869200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>34377900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>35916600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>35595400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>35234100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>33619000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>31945900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>31483000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>31732800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>30464800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>30961600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>32753800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>32431700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>32729100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>32594100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>29991300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>28820300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>29053200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>28244400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>29954000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>29674300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>28662700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>28192300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>27898200</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>26714100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8475,257 +8663,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1286400</v>
+      </c>
+      <c r="E81" s="3">
         <v>1243200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>492800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1200200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1284500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1152500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>463100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1233200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1257200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>775300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>168400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1016900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1138100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1157100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>55500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>973300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>862300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1092900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>462800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>958700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>889800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>929700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>429800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>893200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>753500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>588200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>451700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>796500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>872200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>769500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>161600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>772600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>795300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>813300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>487300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>789800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>871300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>783100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1929400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8768,130 +8965,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>164900</v>
+      </c>
+      <c r="E83" s="3">
         <v>152000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-1200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>176800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>164600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>161400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-45400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>160900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>160500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>157600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>28500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>144100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>152200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>156200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>202400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>186900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>181300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>184100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>200000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>189300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>175200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>188000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>209100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>201000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>191400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>207800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>231500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>206200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>206400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>206800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>151600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>125800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>122400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>119500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>149900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>136300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>132700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>67000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>260500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>63400</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9012,8 +9213,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9134,8 +9338,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9256,8 +9463,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9378,8 +9588,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9500,130 +9713,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7370100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1994500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2060300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8481100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6372300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3115900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5814400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5899300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1622900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-912900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6723200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-666000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2223600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3417900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7145400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-198600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1687000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-956200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2895200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1107500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-472200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2728400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1929300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>549500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-6976500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-475300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-174900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>234800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2876700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>5515700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>761100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-812100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2053300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-5390100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1653000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-1521200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-3347200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-1063900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1012500</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-288400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9666,130 +9885,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-36200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-29700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-79000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-54400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-84100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-109700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-61300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-44300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-123500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-62800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-54300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-189462000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-139530000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-86262000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-82218000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-197211000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-91912000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-25000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-44000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-105500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-89900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-64500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-66200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-231300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-93500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-123800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-78300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-168700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-121400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-85000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-96500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-83900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-56500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-45900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-457900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-124600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9910,8 +10133,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10032,130 +10258,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1949500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-874100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2933600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-797200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>486200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-571300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-265400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2235300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2153700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2530700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1158400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2780000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1880700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>3222700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6486900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2557600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2382900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3206300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>228300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2168200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2584600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1610700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-959500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4139700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-861500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2589300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3697000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3778800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-432900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2773200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3535000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>903400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1110300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3230100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2307500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1878600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-271700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-3994700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1862000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10198,59 +10430,60 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>659200</v>
+      </c>
+      <c r="E96" s="3">
         <v>29400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>265400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>274500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>507100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>33700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>236600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>266200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>681800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>35800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>187400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>181300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>614200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>31200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-146100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-142200</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -10258,11 +10491,11 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-219200</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -10279,14 +10512,14 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>2800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -10315,13 +10548,16 @@
         <v>0</v>
       </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-340800</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10442,8 +10678,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10564,8 +10803,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10686,370 +10928,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15206900</v>
+      </c>
+      <c r="E100" s="3">
         <v>801100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>10589400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2808100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8575400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1282400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>7499000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3943600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3970500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6333200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4467900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5957500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-8526100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>86000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2307900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4898100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4052700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2993000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1929500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2504100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>680200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3033600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4276800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>7042500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5234600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4308800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3386300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2312000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3774800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>3142000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>287400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2957600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>3467100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1837500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>5261900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>5424500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>411300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>2863200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>2697200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-247300</v>
+      </c>
+      <c r="E101" s="3">
         <v>65500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>268100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-106900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>108600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>123300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-95100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>18700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>13400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>16900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-227500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>208900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>101900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>42200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-214600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>219000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>96400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>39000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>6200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>53000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-16400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>74900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-75900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-37700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-79000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>66700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-39900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>75100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-39600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>127900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-34400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-41500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>16600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>3800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-63600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-71800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>60800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-43500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>80200</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-16600</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5989800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1834600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5635800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6395200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2442000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1327700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1687200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3779300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>275600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>650200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1643500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1040700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1866600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1868600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>131900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>283200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>306000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-71200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>332300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>921800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-569100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-362500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>68800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>648900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-874400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2236600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>397100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-82600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>92200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-904400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>333700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>337200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-189400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1974100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>196800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1361300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>259500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-967800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-38800</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>530100</v>
       </c>
     </row>
